--- a/05_Figures/F04_association/modules/c_data/F04_modules_source_data.xlsx
+++ b/05_Figures/F04_association/modules/c_data/F04_modules_source_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t xml:space="preserve">feature</t>
   </si>
@@ -40,6 +40,9 @@
     <t xml:space="preserve">n_annotated</t>
   </si>
   <si>
+    <t xml:space="preserve">fry_fdr</t>
+  </si>
+  <si>
     <t xml:space="preserve">ME_black</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t xml:space="preserve">ME_red</t>
   </si>
   <si>
+    <t xml:space="preserve">ME_tan</t>
+  </si>
+  <si>
     <t xml:space="preserve">ME_turquoise</t>
   </si>
   <si>
@@ -131,33 +137,33 @@
   </si>
   <si>
     <t xml:space="preserve">blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNA splicing, via
-transesterification
-rea...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blue - RNA Splicing*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteinogenic amino
-acid metabolic process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brown - Amino Acid Metabolism</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yellow</t>
   </si>
   <si>
     <t xml:space="preserve">small molecule
 metabolic process</t>
   </si>
   <si>
+    <t xml:space="preserve">Blue - RNA Splicing*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cytoskeleton
+organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brown - Amino Acid Metabolism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">energy derivation
+by oxidation of
+organic...</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yellow - Small-Molecule Metabolism</t>
   </si>
   <si>
@@ -176,49 +182,53 @@
     <t xml:space="preserve">black</t>
   </si>
   <si>
-    <t xml:space="preserve">aerobic respiration</t>
-  </si>
-  <si>
     <t xml:space="preserve">Black - Aerobic Respiration</t>
   </si>
   <si>
     <t xml:space="preserve">pink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">actin filament-based
+process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pink - Cytoplasmic Translation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">magenta</t>
   </si>
   <si>
     <t xml:space="preserve">cytoplasmic
 translation</t>
   </si>
   <si>
-    <t xml:space="preserve">Pink - Cytoplasmic Translation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">magenta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">actin filament-based
-process</t>
-  </si>
-  <si>
     <t xml:space="preserve">Magenta - Sarcomere / Myofibril</t>
   </si>
   <si>
     <t xml:space="preserve">purple</t>
   </si>
   <si>
-    <t xml:space="preserve">translation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Purple - Translation (secondary)</t>
   </si>
   <si>
     <t xml:space="preserve">greenyellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">extracellular matrix
+organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greenyellow - Electron Transport Chain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tan</t>
   </si>
   <si>
     <t xml:space="preserve">aerobic electron
 transport chain</t>
   </si>
   <si>
-    <t xml:space="preserve">Greenyellow - Electron Transport Chain</t>
+    <t xml:space="preserve">Tan</t>
   </si>
 </sst>
 </file>
@@ -572,292 +582,308 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.17425092658077</v>
+        <v>0.106679111156521</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0204071679468525</v>
+        <v>0.159814159212223</v>
       </c>
       <c r="F2" t="n">
-        <v>0.224478847415378</v>
+        <v>0.351742465640986</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
+      <c r="I2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
       <c r="D3" t="n">
-        <v>0.00461843191688611</v>
+        <v>0.0164998065356796</v>
       </c>
       <c r="E3" t="n">
-        <v>0.950840679229933</v>
+        <v>0.827709455629325</v>
       </c>
       <c r="F3" t="n">
-        <v>0.960146595097477</v>
+        <v>0.978294435788638</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
+      <c r="I3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.145404468260077</v>
+        <v>0.00065224547308039</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0527756256599646</v>
+        <v>0.993135371570823</v>
       </c>
       <c r="F4" t="n">
-        <v>0.255336764787751</v>
+        <v>0.993135371570823</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
+      <c r="I4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.119870424819134</v>
+        <v>0.0840181310144708</v>
       </c>
       <c r="E5" t="n">
-        <v>0.110095794873296</v>
+        <v>0.268060550348461</v>
       </c>
       <c r="F5" t="n">
-        <v>0.255336764787751</v>
+        <v>0.459532372025933</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
+      <c r="I5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0695662929791277</v>
+        <v>0.0160367928499266</v>
       </c>
       <c r="E6" t="n">
-        <v>0.35331903045467</v>
+        <v>0.832471279931623</v>
       </c>
       <c r="F6" t="n">
-        <v>0.485813666875172</v>
+        <v>0.978294435788638</v>
       </c>
       <c r="G6"/>
       <c r="H6"/>
+      <c r="I6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.102069989661726</v>
+        <v>0.00983594256126937</v>
       </c>
       <c r="E7" t="n">
-        <v>0.17349609883131</v>
+        <v>0.896769899472918</v>
       </c>
       <c r="F7" t="n">
-        <v>0.318076181190734</v>
+        <v>0.978294435788638</v>
       </c>
       <c r="G7"/>
       <c r="H7"/>
+      <c r="I7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0182622226962919</v>
+        <v>-0.102715834816381</v>
       </c>
       <c r="E8" t="n">
-        <v>0.807406522566315</v>
+        <v>0.175871232820493</v>
       </c>
       <c r="F8" t="n">
-        <v>0.960146595097477</v>
+        <v>0.351742465640986</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
+      <c r="I8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>0.125170010431124</v>
+        <v>0.1052517143198</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0952805350550737</v>
+        <v>0.165463982982672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.255336764787751</v>
+        <v>0.351742465640986</v>
       </c>
       <c r="G9"/>
       <c r="H9"/>
+      <c r="I9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0872939501086421</v>
+        <v>-0.118090119538363</v>
       </c>
       <c r="E10" t="n">
-        <v>0.244277496561677</v>
+        <v>0.119782193577689</v>
       </c>
       <c r="F10" t="n">
-        <v>0.383864637454063</v>
+        <v>0.351742465640986</v>
       </c>
       <c r="G10"/>
       <c r="H10"/>
+      <c r="I10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.117895785723807</v>
+        <v>0.0703905355048749</v>
       </c>
       <c r="E11" t="n">
-        <v>0.116062165812614</v>
+        <v>0.353365966225374</v>
       </c>
       <c r="F11" t="n">
-        <v>0.255336764787751</v>
+        <v>0.530048949338061</v>
       </c>
       <c r="G11"/>
       <c r="H11"/>
+      <c r="I11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0037433413698872</v>
+        <v>-0.115775266535295</v>
       </c>
       <c r="E12" t="n">
-        <v>0.960146595097477</v>
+        <v>0.127191848392785</v>
       </c>
       <c r="F12" t="n">
-        <v>0.960146595097477</v>
+        <v>0.351742465640986</v>
       </c>
       <c r="G12"/>
       <c r="H12"/>
+      <c r="I12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0887187279761334</v>
+        <v>0.17673132101363</v>
       </c>
       <c r="E13" t="n">
-        <v>0.202292779264323</v>
+        <v>0.0200988864856963</v>
       </c>
       <c r="F13" t="n">
-        <v>0.950327173765851</v>
+        <v>0.241186637828355</v>
       </c>
       <c r="G13"/>
       <c r="H13"/>
+      <c r="I13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00664479106411173</v>
+        <v>0.00620750615759553</v>
       </c>
       <c r="E14" t="n">
-        <v>0.923848085773366</v>
+        <v>0.929700041547618</v>
       </c>
       <c r="F14" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G14"/>
       <c r="H14"/>
+      <c r="I14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -867,19 +893,20 @@
         <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0113712482267952</v>
+        <v>0.00713761272197522</v>
       </c>
       <c r="E15" t="n">
-        <v>0.870063610774027</v>
+        <v>0.91920042888924</v>
       </c>
       <c r="F15" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G15"/>
       <c r="H15"/>
+      <c r="I15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -889,19 +916,20 @@
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.00433049874317533</v>
+        <v>0.0296371350882687</v>
       </c>
       <c r="E16" t="n">
-        <v>0.950327173765851</v>
+        <v>0.673630717139674</v>
       </c>
       <c r="F16" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G16"/>
       <c r="H16"/>
+      <c r="I16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -911,19 +939,20 @@
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0154778749012223</v>
+        <v>-0.036607693468954</v>
       </c>
       <c r="E17" t="n">
-        <v>0.823808406517541</v>
+        <v>0.602922594060989</v>
       </c>
       <c r="F17" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G17"/>
       <c r="H17"/>
+      <c r="I17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -933,19 +962,20 @@
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.00666295405271881</v>
+        <v>-0.0168770929595755</v>
       </c>
       <c r="E18" t="n">
-        <v>0.92364056880673</v>
+        <v>0.810443423226343</v>
       </c>
       <c r="F18" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G18"/>
       <c r="H18"/>
+      <c r="I18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -955,19 +985,20 @@
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0133069405380289</v>
+        <v>0.00513284709983518</v>
       </c>
       <c r="E19" t="n">
-        <v>0.848195058698829</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="F19" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G19"/>
       <c r="H19"/>
+      <c r="I19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -977,19 +1008,20 @@
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D20" t="n">
-        <v>0.023496990295322</v>
+        <v>-0.00682196906601559</v>
       </c>
       <c r="E20" t="n">
-        <v>0.735369463411301</v>
+        <v>0.922762116749113</v>
       </c>
       <c r="F20" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G20"/>
       <c r="H20"/>
+      <c r="I20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -999,19 +1031,20 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00479271567000719</v>
+        <v>0.0382418583576679</v>
       </c>
       <c r="E21" t="n">
-        <v>0.94503334984807</v>
+        <v>0.586842790792824</v>
       </c>
       <c r="F21" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G21"/>
       <c r="H21"/>
+      <c r="I21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
@@ -1021,19 +1054,20 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0207367056611498</v>
+        <v>-0.00735778018481538</v>
       </c>
       <c r="E22" t="n">
-        <v>0.765481190564536</v>
+        <v>0.916717041909098</v>
       </c>
       <c r="F22" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G22"/>
       <c r="H22"/>
+      <c r="I22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
@@ -1043,1713 +1077,1998 @@
         <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0177842856521897</v>
+        <v>0.0165351194725005</v>
       </c>
       <c r="E23" t="n">
-        <v>0.798086166305484</v>
+        <v>0.814213193755719</v>
       </c>
       <c r="F23" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G23"/>
       <c r="H23"/>
+      <c r="I23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.134267572014771</v>
+        <v>-0.0185968615643766</v>
       </c>
       <c r="E24" t="n">
-        <v>0.071337504857376</v>
+        <v>0.79155391705199</v>
       </c>
       <c r="F24" t="n">
-        <v>0.156942510686227</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G24"/>
       <c r="H24"/>
+      <c r="I24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D25" t="n">
-        <v>0.138659313379964</v>
+        <v>0.0728360080369906</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0625927404040017</v>
+        <v>0.300869324970724</v>
       </c>
       <c r="F25" t="n">
-        <v>0.156942510686227</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G25"/>
       <c r="H25"/>
+      <c r="I25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.201537382986135</v>
+        <v>-0.0282479596820163</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00692506393730139</v>
+        <v>0.707281475434882</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0761757033103153</v>
+        <v>0.707281475434882</v>
       </c>
       <c r="G26"/>
       <c r="H26"/>
+      <c r="I26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0860009796394341</v>
+        <v>-0.174783134081328</v>
       </c>
       <c r="E27" t="n">
-        <v>0.24753585628794</v>
+        <v>0.0205059050658457</v>
       </c>
       <c r="F27" t="n">
-        <v>0.45381573652789</v>
+        <v>0.0823720753199149</v>
       </c>
       <c r="G27"/>
       <c r="H27"/>
+      <c r="I27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0756058703989498</v>
+        <v>0.157032962373461</v>
       </c>
       <c r="E28" t="n">
-        <v>0.309265558677127</v>
+        <v>0.0372686188618791</v>
       </c>
       <c r="F28" t="n">
-        <v>0.485988735064057</v>
+        <v>0.111805856585637</v>
       </c>
       <c r="G28"/>
       <c r="H28"/>
+      <c r="I28"/>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0580905756380288</v>
+        <v>-0.140563115139643</v>
       </c>
       <c r="E29" t="n">
-        <v>0.434562721128356</v>
+        <v>0.0621507392549162</v>
       </c>
       <c r="F29" t="n">
-        <v>0.531132214712436</v>
+        <v>0.149161774211799</v>
       </c>
       <c r="G29"/>
       <c r="H29"/>
+      <c r="I29"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D30" t="n">
-        <v>0.172240437979974</v>
+        <v>-0.0482262037767428</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0208598776799607</v>
+        <v>0.52152614633427</v>
       </c>
       <c r="F30" t="n">
-        <v>0.076486218159856</v>
+        <v>0.625831375601124</v>
       </c>
       <c r="G30"/>
       <c r="H30"/>
+      <c r="I30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.012242707258276</v>
+        <v>0.182486265530603</v>
       </c>
       <c r="E31" t="n">
-        <v>0.869149151821834</v>
+        <v>0.0155867197126552</v>
       </c>
       <c r="F31" t="n">
-        <v>0.869149151821834</v>
+        <v>0.0823720753199149</v>
       </c>
       <c r="G31"/>
       <c r="H31"/>
+      <c r="I31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.032247605111012</v>
+        <v>0.0616244307168021</v>
       </c>
       <c r="E32" t="n">
-        <v>0.664370598154253</v>
+        <v>0.412807914786857</v>
       </c>
       <c r="F32" t="n">
-        <v>0.730807657969679</v>
+        <v>0.550410553049142</v>
       </c>
       <c r="G32"/>
       <c r="H32"/>
+      <c r="I32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0663536601440665</v>
+        <v>0.0294183913497299</v>
       </c>
       <c r="E33" t="n">
-        <v>0.372145270872292</v>
+        <v>0.695748382816483</v>
       </c>
       <c r="F33" t="n">
-        <v>0.511699747449401</v>
+        <v>0.707281475434882</v>
       </c>
       <c r="G33"/>
       <c r="H33"/>
+      <c r="I33"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.182328952689138</v>
+        <v>0.0933746546791991</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0144880606336468</v>
+        <v>0.214852102760389</v>
       </c>
       <c r="F34" t="n">
-        <v>0.076486218159856</v>
+        <v>0.429704205520778</v>
       </c>
       <c r="G34"/>
       <c r="H34"/>
+      <c r="I34"/>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C35" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0229610877851472</v>
+        <v>-0.0859094248008704</v>
       </c>
       <c r="E35" t="n">
-        <v>0.741185386719181</v>
+        <v>0.253739403885517</v>
       </c>
       <c r="F35" t="n">
-        <v>0.815303925391099</v>
+        <v>0.434981835232315</v>
       </c>
       <c r="G35"/>
       <c r="H35"/>
+      <c r="I35"/>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D36" t="n">
-        <v>0.171674155243678</v>
+        <v>0.0638551652923891</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0138594053081593</v>
+        <v>0.396112031180432</v>
       </c>
       <c r="F36" t="n">
-        <v>0.152453458389753</v>
+        <v>0.550410553049142</v>
       </c>
       <c r="G36"/>
       <c r="H36"/>
+      <c r="I36"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C37" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D37" t="n">
-        <v>0.00616101253664516</v>
+        <v>-0.174662039385145</v>
       </c>
       <c r="E37" t="n">
-        <v>0.929377253711649</v>
+        <v>0.0205930188299787</v>
       </c>
       <c r="F37" t="n">
-        <v>0.929377253711649</v>
+        <v>0.0823720753199149</v>
       </c>
       <c r="G37"/>
       <c r="H37"/>
+      <c r="I37"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0877014718973078</v>
+        <v>0.130769293679604</v>
       </c>
       <c r="E38" t="n">
-        <v>0.207505651047244</v>
+        <v>0.0635809801719385</v>
       </c>
       <c r="F38" t="n">
-        <v>0.540898714652634</v>
+        <v>0.527193126890309</v>
       </c>
       <c r="G38"/>
       <c r="H38"/>
+      <c r="I38"/>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0435137770911641</v>
+        <v>-0.101639507795085</v>
       </c>
       <c r="E39" t="n">
-        <v>0.531432234719305</v>
+        <v>0.149043568699856</v>
       </c>
       <c r="F39" t="n">
-        <v>0.751880675854233</v>
+        <v>0.596174274799422</v>
       </c>
       <c r="G39"/>
       <c r="H39"/>
+      <c r="I39"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0390834897963618</v>
+        <v>0.12027851759581</v>
       </c>
       <c r="E40" t="n">
-        <v>0.574028137538539</v>
+        <v>0.0878655211483848</v>
       </c>
       <c r="F40" t="n">
-        <v>0.751880675854233</v>
+        <v>0.527193126890309</v>
       </c>
       <c r="G40"/>
       <c r="H40"/>
+      <c r="I40"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D41" t="n">
-        <v>0.034950254340995</v>
+        <v>0.0405545434450909</v>
       </c>
       <c r="E41" t="n">
-        <v>0.615175098426191</v>
+        <v>0.564433489042099</v>
       </c>
       <c r="F41" t="n">
-        <v>0.751880675854233</v>
+        <v>0.752577985389465</v>
       </c>
       <c r="G41"/>
       <c r="H41"/>
+      <c r="I41"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0807323044692387</v>
+        <v>0.0023391557339578</v>
       </c>
       <c r="E42" t="n">
-        <v>0.245863052114834</v>
+        <v>0.973479501870069</v>
       </c>
       <c r="F42" t="n">
-        <v>0.540898714652634</v>
+        <v>0.973479501870069</v>
       </c>
       <c r="G42"/>
       <c r="H42"/>
+      <c r="I42"/>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B43" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D43" t="n">
-        <v>0.086693100125935</v>
+        <v>0.0525217862080328</v>
       </c>
       <c r="E43" t="n">
-        <v>0.212768837336716</v>
+        <v>0.455528287866432</v>
       </c>
       <c r="F43" t="n">
-        <v>0.540898714652634</v>
+        <v>0.752577985389465</v>
       </c>
       <c r="G43"/>
       <c r="H43"/>
+      <c r="I43"/>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0521917982384489</v>
+        <v>0.04523826678797</v>
       </c>
       <c r="E44" t="n">
-        <v>0.452920807250981</v>
+        <v>0.520356892504631</v>
       </c>
       <c r="F44" t="n">
-        <v>0.751880675854233</v>
+        <v>0.752577985389465</v>
       </c>
       <c r="G44"/>
       <c r="H44"/>
+      <c r="I44"/>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.109832299275072</v>
+        <v>0.0430142920971172</v>
       </c>
       <c r="E45" t="n">
-        <v>0.114636651070569</v>
+        <v>0.541062142586273</v>
       </c>
       <c r="F45" t="n">
-        <v>0.540898714652634</v>
+        <v>0.752577985389465</v>
       </c>
       <c r="G45"/>
       <c r="H45"/>
+      <c r="I45"/>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.0824913161283707</v>
+        <v>-0.0870395789449637</v>
       </c>
       <c r="E46" t="n">
-        <v>0.281157166697679</v>
+        <v>0.216452007158174</v>
       </c>
       <c r="F46" t="n">
-        <v>0.817821017702153</v>
+        <v>0.649356021474523</v>
       </c>
       <c r="G46"/>
       <c r="H46"/>
+      <c r="I46"/>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B47" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0380302779130285</v>
+        <v>-0.030434410883923</v>
       </c>
       <c r="E47" t="n">
-        <v>0.619105171121224</v>
+        <v>0.665379442333905</v>
       </c>
       <c r="F47" t="n">
-        <v>0.817821017702153</v>
+        <v>0.798455330800687</v>
       </c>
       <c r="G47"/>
       <c r="H47"/>
+      <c r="I47"/>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.0479359899891019</v>
+        <v>-0.0525746278049512</v>
       </c>
       <c r="E48" t="n">
-        <v>0.530954309851595</v>
+        <v>0.455075235643833</v>
       </c>
       <c r="F48" t="n">
-        <v>0.817821017702153</v>
+        <v>0.752577985389465</v>
       </c>
       <c r="G48"/>
       <c r="H48"/>
+      <c r="I48"/>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B49" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0664936558031391</v>
+        <v>-0.0223069136055875</v>
       </c>
       <c r="E49" t="n">
-        <v>0.384888103779534</v>
+        <v>0.751232738856985</v>
       </c>
       <c r="F49" t="n">
-        <v>0.817821017702153</v>
+        <v>0.81952662420762</v>
       </c>
       <c r="G49"/>
       <c r="H49"/>
+      <c r="I49"/>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C50" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.101254381201523</v>
+        <v>-0.0148843622656003</v>
       </c>
       <c r="E50" t="n">
-        <v>0.186033723986584</v>
+        <v>0.847308229565406</v>
       </c>
       <c r="F50" t="n">
-        <v>0.817821017702153</v>
+        <v>0.951676696031647</v>
       </c>
       <c r="G50"/>
       <c r="H50"/>
+      <c r="I50"/>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D51" t="n">
-        <v>0.055700183525113</v>
+        <v>-0.0518772222493833</v>
       </c>
       <c r="E51" t="n">
-        <v>0.466629583619688</v>
+        <v>0.502239528905025</v>
       </c>
       <c r="F51" t="n">
-        <v>0.817821017702153</v>
+        <v>0.922584841692793</v>
       </c>
       <c r="G51"/>
       <c r="H51"/>
+      <c r="I51"/>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0205292519744194</v>
+        <v>0.0453289188205259</v>
       </c>
       <c r="E52" t="n">
-        <v>0.788407708561996</v>
+        <v>0.557667863955496</v>
       </c>
       <c r="F52" t="n">
-        <v>0.817821017702153</v>
+        <v>0.922584841692793</v>
       </c>
       <c r="G52"/>
       <c r="H52"/>
+      <c r="I52"/>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B53" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.0248568094299941</v>
+        <v>0.00468438006438979</v>
       </c>
       <c r="E53" t="n">
-        <v>0.745221450791998</v>
+        <v>0.951676696031647</v>
       </c>
       <c r="F53" t="n">
-        <v>0.817821017702153</v>
+        <v>0.951676696031647</v>
       </c>
       <c r="G53"/>
       <c r="H53"/>
+      <c r="I53"/>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C54" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.0176199755287301</v>
+        <v>0.0506275924890334</v>
       </c>
       <c r="E54" t="n">
-        <v>0.817821017702153</v>
+        <v>0.512586742383027</v>
       </c>
       <c r="F54" t="n">
-        <v>0.817821017702153</v>
+        <v>0.922584841692793</v>
       </c>
       <c r="G54"/>
       <c r="H54"/>
+      <c r="I54"/>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B55" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C55" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0327548964787683</v>
+        <v>0.00484475146308899</v>
       </c>
       <c r="E55" t="n">
-        <v>0.668522347161275</v>
+        <v>0.950024466849225</v>
       </c>
       <c r="F55" t="n">
-        <v>0.817821017702153</v>
+        <v>0.951676696031647</v>
       </c>
       <c r="G55"/>
       <c r="H55"/>
+      <c r="I55"/>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B56" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C56" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.0398879738502371</v>
+        <v>0.0573564263286989</v>
       </c>
       <c r="E56" t="n">
-        <v>0.602091909135782</v>
+        <v>0.458210053214844</v>
       </c>
       <c r="F56" t="n">
-        <v>0.817821017702153</v>
+        <v>0.922584841692793</v>
       </c>
       <c r="G56"/>
       <c r="H56"/>
+      <c r="I56"/>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C57" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D57" t="n">
-        <v>0.00304088247626602</v>
+        <v>-0.0306300639225915</v>
       </c>
       <c r="E57" t="n">
-        <v>0.968299516204039</v>
+        <v>0.691938631269595</v>
       </c>
       <c r="F57" t="n">
-        <v>0.968299516204039</v>
+        <v>0.922584841692793</v>
       </c>
       <c r="G57"/>
       <c r="H57"/>
+      <c r="I57"/>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B58" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C58" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0360039187658029</v>
+        <v>0.0591895800604847</v>
       </c>
       <c r="E58" t="n">
-        <v>0.638017204278547</v>
+        <v>0.443979077373685</v>
       </c>
       <c r="F58" t="n">
-        <v>0.779798805229336</v>
+        <v>0.922584841692793</v>
       </c>
       <c r="G58"/>
       <c r="H58"/>
+      <c r="I58"/>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B59" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C59" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0860972300441796</v>
+        <v>-0.0881528900574695</v>
       </c>
       <c r="E59" t="n">
-        <v>0.260855560091162</v>
+        <v>0.25443820157249</v>
       </c>
       <c r="F59" t="n">
-        <v>0.779798805229336</v>
+        <v>0.922584841692793</v>
       </c>
       <c r="G59"/>
       <c r="H59"/>
+      <c r="I59"/>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.0490462702728194</v>
+        <v>0.0325143262666986</v>
       </c>
       <c r="E60" t="n">
-        <v>0.521633130972589</v>
+        <v>0.674050403715883</v>
       </c>
       <c r="F60" t="n">
-        <v>0.779798805229336</v>
+        <v>0.922584841692793</v>
       </c>
       <c r="G60"/>
       <c r="H60"/>
+      <c r="I60"/>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.0471659631236178</v>
+        <v>-0.0954318394594336</v>
       </c>
       <c r="E61" t="n">
-        <v>0.53771412692509</v>
+        <v>0.217355661629767</v>
       </c>
       <c r="F61" t="n">
-        <v>0.779798805229336</v>
+        <v>0.922584841692793</v>
       </c>
       <c r="G61"/>
       <c r="H61"/>
+      <c r="I61"/>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.0397068520838941</v>
+        <v>0.0855872427333253</v>
       </c>
       <c r="E62" t="n">
-        <v>0.603868400994964</v>
+        <v>0.268665968550084</v>
       </c>
       <c r="F62" t="n">
-        <v>0.779798805229336</v>
+        <v>0.876530916682701</v>
       </c>
       <c r="G62"/>
       <c r="H62"/>
+      <c r="I62"/>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C63" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0254845341326823</v>
+        <v>-0.042515028435679</v>
       </c>
       <c r="E63" t="n">
-        <v>0.739108082512013</v>
+        <v>0.582497583848994</v>
       </c>
       <c r="F63" t="n">
-        <v>0.813018890763214</v>
+        <v>0.876530916682701</v>
       </c>
       <c r="G63"/>
       <c r="H63"/>
+      <c r="I63"/>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0768162107058077</v>
+        <v>0.0163440292053376</v>
       </c>
       <c r="E64" t="n">
-        <v>0.315707331909155</v>
+        <v>0.832602132286803</v>
       </c>
       <c r="F64" t="n">
-        <v>0.779798805229336</v>
+        <v>0.912842521828395</v>
       </c>
       <c r="G64"/>
       <c r="H64"/>
+      <c r="I64"/>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B65" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0648812589099049</v>
+        <v>0.125310204547815</v>
       </c>
       <c r="E65" t="n">
-        <v>0.39667468693565</v>
+        <v>0.105594594279685</v>
       </c>
       <c r="F65" t="n">
-        <v>0.779798805229336</v>
+        <v>0.876530916682701</v>
       </c>
       <c r="G65"/>
       <c r="H65"/>
+      <c r="I65"/>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C66" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.064404183583889</v>
+        <v>0.0835414782985354</v>
       </c>
       <c r="E66" t="n">
-        <v>0.400153048945474</v>
+        <v>0.280260856494352</v>
       </c>
       <c r="F66" t="n">
-        <v>0.779798805229336</v>
+        <v>0.876530916682701</v>
       </c>
       <c r="G66"/>
       <c r="H66"/>
+      <c r="I66"/>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B67" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C67" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.0539289181325395</v>
+        <v>0.00954784692452318</v>
       </c>
       <c r="E67" t="n">
-        <v>0.481065066356249</v>
+        <v>0.901729153445781</v>
       </c>
       <c r="F67" t="n">
-        <v>0.779798805229336</v>
+        <v>0.912842521828395</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
+      <c r="I67"/>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B68" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.108265601753358</v>
+        <v>-0.0385374394216661</v>
       </c>
       <c r="E68" t="n">
-        <v>0.157576284908472</v>
+        <v>0.618256840135387</v>
       </c>
       <c r="F68" t="n">
-        <v>0.346667826798639</v>
+        <v>0.876530916682701</v>
       </c>
       <c r="G68"/>
       <c r="H68"/>
+      <c r="I68"/>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C69" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D69" t="n">
-        <v>0.00298907690208906</v>
+        <v>0.0363797920395403</v>
       </c>
       <c r="E69" t="n">
-        <v>0.968839299111306</v>
+        <v>0.638048601066119</v>
       </c>
       <c r="F69" t="n">
-        <v>0.968839299111306</v>
+        <v>0.876530916682701</v>
       </c>
       <c r="G69"/>
       <c r="H69"/>
+      <c r="I69"/>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B70" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C70" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.121601165478601</v>
+        <v>-0.0515427592930625</v>
       </c>
       <c r="E70" t="n">
-        <v>0.112542877714915</v>
+        <v>0.505141010626103</v>
       </c>
       <c r="F70" t="n">
-        <v>0.309492913716018</v>
+        <v>0.876530916682701</v>
       </c>
       <c r="G70"/>
       <c r="H70"/>
+      <c r="I70"/>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B71" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C71" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D71" t="n">
-        <v>0.124656181263922</v>
+        <v>-0.0342974740250952</v>
       </c>
       <c r="E71" t="n">
-        <v>0.103819433855277</v>
+        <v>0.657398187512026</v>
       </c>
       <c r="F71" t="n">
-        <v>0.309492913716018</v>
+        <v>0.876530916682701</v>
       </c>
       <c r="G71"/>
       <c r="H71"/>
+      <c r="I71"/>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C72" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.0792580564314036</v>
+        <v>-0.0646640787042194</v>
       </c>
       <c r="E72" t="n">
-        <v>0.300588282377239</v>
+        <v>0.403176861067897</v>
       </c>
       <c r="F72" t="n">
-        <v>0.551078517691606</v>
+        <v>0.876530916682701</v>
       </c>
       <c r="G72"/>
       <c r="H72"/>
+      <c r="I72"/>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B73" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C73" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.0206997662422272</v>
+        <v>0.00846347351720542</v>
       </c>
       <c r="E73" t="n">
-        <v>0.786765779684009</v>
+        <v>0.912842521828395</v>
       </c>
       <c r="F73" t="n">
-        <v>0.916027362498677</v>
+        <v>0.912842521828395</v>
       </c>
       <c r="G73"/>
       <c r="H73"/>
+      <c r="I73"/>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C74" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D74" t="n">
-        <v>0.162774717771661</v>
+        <v>-0.0734300106282945</v>
       </c>
       <c r="E74" t="n">
-        <v>0.033861927042385</v>
+        <v>0.342527989573741</v>
       </c>
       <c r="F74" t="n">
-        <v>0.309492913716018</v>
+        <v>0.671068819551934</v>
       </c>
       <c r="G74"/>
       <c r="H74"/>
+      <c r="I74"/>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C75" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.016158801021707</v>
+        <v>-0.115658654721923</v>
       </c>
       <c r="E75" t="n">
-        <v>0.83275214772607</v>
+        <v>0.13518077973217</v>
       </c>
       <c r="F75" t="n">
-        <v>0.916027362498677</v>
+        <v>0.405542339196511</v>
       </c>
       <c r="G75"/>
       <c r="H75"/>
+      <c r="I75"/>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C76" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.0540594463270421</v>
+        <v>0.0530984739829882</v>
       </c>
       <c r="E76" t="n">
-        <v>0.480004729514559</v>
+        <v>0.492380681121931</v>
       </c>
       <c r="F76" t="n">
-        <v>0.660006503082519</v>
+        <v>0.671068819551934</v>
       </c>
       <c r="G76"/>
       <c r="H76"/>
+      <c r="I76"/>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0541412747986264</v>
+        <v>-0.055807454036919</v>
       </c>
       <c r="E77" t="n">
-        <v>0.47934065424041</v>
+        <v>0.470581328112939</v>
       </c>
       <c r="F77" t="n">
-        <v>0.660006503082519</v>
+        <v>0.671068819551934</v>
       </c>
       <c r="G77"/>
       <c r="H77"/>
+      <c r="I77"/>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B78" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C78" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.126425571546606</v>
+        <v>0.0329761187878349</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0990190003951576</v>
+        <v>0.669798293359957</v>
       </c>
       <c r="F78" t="n">
-        <v>0.309492913716018</v>
+        <v>0.774525374998041</v>
       </c>
       <c r="G78"/>
       <c r="H78"/>
+      <c r="I78"/>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B79" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C79" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0855321986046367</v>
+        <v>0.139512326247094</v>
       </c>
       <c r="E79" t="n">
-        <v>0.402819725128278</v>
+        <v>0.0716830412962833</v>
       </c>
       <c r="F79" t="n">
-        <v>0.65950051515095</v>
+        <v>0.384311055119259</v>
       </c>
       <c r="G79"/>
       <c r="H79"/>
+      <c r="I79"/>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B80" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C80" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.00202635914722561</v>
+        <v>-0.022151275492834</v>
       </c>
       <c r="E80" t="n">
-        <v>0.984180550172677</v>
+        <v>0.774525374998041</v>
       </c>
       <c r="F80" t="n">
-        <v>0.984180550172677</v>
+        <v>0.774525374998041</v>
       </c>
       <c r="G80"/>
       <c r="H80"/>
+      <c r="I80"/>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B81" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C81" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D81" t="n">
-        <v>0.134033220033281</v>
+        <v>0.022783891292153</v>
       </c>
       <c r="E81" t="n">
-        <v>0.190124840249583</v>
+        <v>0.76826826393477</v>
       </c>
       <c r="F81" t="n">
-        <v>0.65950051515095</v>
+        <v>0.774525374998041</v>
       </c>
       <c r="G81"/>
       <c r="H81"/>
+      <c r="I81"/>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B82" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C82" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.115539926075959</v>
+        <v>0.1288714743311</v>
       </c>
       <c r="E82" t="n">
-        <v>0.258592783785286</v>
+        <v>0.0960777637798146</v>
       </c>
       <c r="F82" t="n">
-        <v>0.65950051515095</v>
+        <v>0.384311055119259</v>
       </c>
       <c r="G82"/>
       <c r="H82"/>
+      <c r="I82"/>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B83" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C83" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D83" t="n">
-        <v>0.0540884180779053</v>
+        <v>-0.0897724879420425</v>
       </c>
       <c r="E83" t="n">
-        <v>0.596686197717115</v>
+        <v>0.245985886443367</v>
       </c>
       <c r="F83" t="n">
-        <v>0.820443521861032</v>
+        <v>0.590366127464082</v>
       </c>
       <c r="G83"/>
       <c r="H83"/>
+      <c r="I83"/>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B84" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C84" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.0954070356090071</v>
+        <v>0.0517657143931209</v>
       </c>
       <c r="E84" t="n">
-        <v>0.35077381883406</v>
+        <v>0.503301614663951</v>
       </c>
       <c r="F84" t="n">
-        <v>0.65950051515095</v>
+        <v>0.671068819551934</v>
       </c>
       <c r="G84"/>
       <c r="H84"/>
+      <c r="I84"/>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B85" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C85" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D85" t="n">
-        <v>0.00495528215826297</v>
+        <v>-0.143891652262352</v>
       </c>
       <c r="E85" t="n">
-        <v>0.961327597329494</v>
+        <v>0.063245917851087</v>
       </c>
       <c r="F85" t="n">
-        <v>0.984180550172677</v>
+        <v>0.384311055119259</v>
       </c>
       <c r="G85"/>
       <c r="H85"/>
+      <c r="I85"/>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C86" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D86" t="n">
-        <v>0.101673020135802</v>
+        <v>0.100471604998926</v>
       </c>
       <c r="E86" t="n">
-        <v>0.320075462248847</v>
+        <v>0.331599736894066</v>
       </c>
       <c r="F86" t="n">
-        <v>0.65950051515095</v>
+        <v>0.708162829885467</v>
       </c>
       <c r="G86"/>
       <c r="H86"/>
+      <c r="I86"/>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B87" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C87" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D87" t="n">
-        <v>0.0825012344386349</v>
+        <v>0.00936219381370434</v>
       </c>
       <c r="E87" t="n">
-        <v>0.41968214600515</v>
+        <v>0.927877351922577</v>
       </c>
       <c r="F87" t="n">
-        <v>0.65950051515095</v>
+        <v>0.96373210668647</v>
       </c>
       <c r="G87"/>
       <c r="H87"/>
+      <c r="I87"/>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C88" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.0971590800626574</v>
+        <v>-0.0289848896151883</v>
       </c>
       <c r="E88" t="n">
-        <v>0.342007253225118</v>
+        <v>0.779307298309783</v>
       </c>
       <c r="F88" t="n">
-        <v>0.65950051515095</v>
+        <v>0.93516875797174</v>
       </c>
       <c r="G88"/>
       <c r="H88"/>
+      <c r="I88"/>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.0140409442823025</v>
+        <v>0.120625824483425</v>
       </c>
       <c r="E89" t="n">
-        <v>0.890722570103284</v>
+        <v>0.243858820361034</v>
       </c>
       <c r="F89" t="n">
-        <v>0.984180550172677</v>
+        <v>0.708162829885467</v>
       </c>
       <c r="G89"/>
       <c r="H89"/>
+      <c r="I89"/>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B90" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C90" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.111306484229624</v>
+        <v>0.0329138858095021</v>
       </c>
       <c r="E90" t="n">
-        <v>0.274367664727275</v>
+        <v>0.750330975512539</v>
       </c>
       <c r="F90" t="n">
-        <v>0.503007385333338</v>
+        <v>0.93516875797174</v>
       </c>
       <c r="G90"/>
       <c r="H90"/>
+      <c r="I90"/>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B91" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C91" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.0330148418637138</v>
+        <v>0.00470309546143418</v>
       </c>
       <c r="E91" t="n">
-        <v>0.745619496610592</v>
+        <v>0.96373210668647</v>
       </c>
       <c r="F91" t="n">
-        <v>0.827741812715881</v>
+        <v>0.96373210668647</v>
       </c>
       <c r="G91"/>
       <c r="H91"/>
+      <c r="I91"/>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B92" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C92" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.20769839552278</v>
+        <v>-0.095893865750365</v>
       </c>
       <c r="E92" t="n">
-        <v>0.0417360760492035</v>
+        <v>0.354081414942733</v>
       </c>
       <c r="F92" t="n">
-        <v>0.459096836541238</v>
+        <v>0.708162829885467</v>
       </c>
       <c r="G92"/>
       <c r="H92"/>
+      <c r="I92"/>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B93" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C93" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D93" t="n">
-        <v>0.173702451536742</v>
+        <v>0.0670098559621318</v>
       </c>
       <c r="E93" t="n">
-        <v>0.0883617586478161</v>
+        <v>0.517163614377893</v>
       </c>
       <c r="F93" t="n">
-        <v>0.485989672562989</v>
+        <v>0.886566196076388</v>
       </c>
       <c r="G93"/>
       <c r="H93"/>
+      <c r="I93"/>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B94" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C94" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.0320920933077857</v>
+        <v>-0.110732339353547</v>
       </c>
       <c r="E94" t="n">
-        <v>0.752492557014437</v>
+        <v>0.284648787287383</v>
       </c>
       <c r="F94" t="n">
-        <v>0.827741812715881</v>
+        <v>0.708162829885467</v>
       </c>
       <c r="G94"/>
       <c r="H94"/>
+      <c r="I94"/>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B95" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C95" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D95" t="n">
-        <v>0.0190070858416669</v>
+        <v>0.0538554160323744</v>
       </c>
       <c r="E95" t="n">
-        <v>0.851832312336532</v>
+        <v>0.602636367404753</v>
       </c>
       <c r="F95" t="n">
-        <v>0.851832312336532</v>
+        <v>0.903954551107129</v>
       </c>
       <c r="G95"/>
       <c r="H95"/>
+      <c r="I95"/>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C96" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D96" t="n">
-        <v>0.137290183638979</v>
+        <v>-0.097178404970918</v>
       </c>
       <c r="E96" t="n">
-        <v>0.177742871318337</v>
+        <v>0.347677514706437</v>
       </c>
       <c r="F96" t="n">
-        <v>0.503007385333338</v>
+        <v>0.708162829885467</v>
       </c>
       <c r="G96"/>
       <c r="H96"/>
+      <c r="I96"/>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B97" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C97" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.0929750117275147</v>
+        <v>0.103895312976639</v>
       </c>
       <c r="E97" t="n">
-        <v>0.361120643427405</v>
+        <v>0.315404517029433</v>
       </c>
       <c r="F97" t="n">
-        <v>0.567475296814493</v>
+        <v>0.708162829885467</v>
       </c>
       <c r="G97"/>
       <c r="H97"/>
+      <c r="I97"/>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B98" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C98" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.118940705236947</v>
+        <v>-0.15901725336162</v>
       </c>
       <c r="E98" t="n">
-        <v>0.242841351016825</v>
+        <v>0.123096282731459</v>
       </c>
       <c r="F98" t="n">
-        <v>0.503007385333338</v>
+        <v>0.418656058555944</v>
       </c>
       <c r="G98"/>
       <c r="H98"/>
+      <c r="I98"/>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B99" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C99" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D99" t="n">
-        <v>0.118545458382515</v>
+        <v>-0.0731436262862439</v>
       </c>
       <c r="E99" t="n">
-        <v>0.244408064073736</v>
+        <v>0.477737376897154</v>
       </c>
       <c r="F99" t="n">
-        <v>0.503007385333338</v>
+        <v>0.818978360395121</v>
       </c>
       <c r="G99"/>
       <c r="H99"/>
+      <c r="I99"/>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C100" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.0724966534140664</v>
+        <v>0.0367544447776506</v>
       </c>
       <c r="E100" t="n">
-        <v>0.476327162749557</v>
+        <v>0.721228266060265</v>
       </c>
       <c r="F100" t="n">
-        <v>0.654949848780641</v>
+        <v>0.865473919272318</v>
       </c>
       <c r="G100"/>
       <c r="H100"/>
+      <c r="I100"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>13</v>
+      </c>
+      <c r="B101" t="s">
+        <v>13</v>
+      </c>
+      <c r="C101" t="s">
+        <v>29</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-0.181117658584734</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.0791668720684252</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.418656058555944</v>
+      </c>
+      <c r="G101"/>
+      <c r="H101"/>
+      <c r="I101"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>14</v>
+      </c>
+      <c r="B102" t="s">
+        <v>14</v>
+      </c>
+      <c r="C102" t="s">
+        <v>29</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-0.0505653595107006</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.623520974891628</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.831361299855504</v>
+      </c>
+      <c r="G102"/>
+      <c r="H102"/>
+      <c r="I102"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>15</v>
+      </c>
+      <c r="C103" t="s">
+        <v>29</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.12996447932257</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.207406635967208</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.4977759263213</v>
+      </c>
+      <c r="G103"/>
+      <c r="H103"/>
+      <c r="I103"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>16</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="s">
+        <v>29</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.0163861639288321</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.873599509560133</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.894985223087413</v>
+      </c>
+      <c r="G104"/>
+      <c r="H104"/>
+      <c r="I104"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>17</v>
+      </c>
+      <c r="B105" t="s">
+        <v>17</v>
+      </c>
+      <c r="C105" t="s">
+        <v>29</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-0.0135959007473873</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.894985223087413</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.894985223087413</v>
+      </c>
+      <c r="G105"/>
+      <c r="H105"/>
+      <c r="I105"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>18</v>
+      </c>
+      <c r="B106" t="s">
+        <v>18</v>
+      </c>
+      <c r="C106" t="s">
+        <v>29</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.180414233624163</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.0803351456903422</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.418656058555944</v>
+      </c>
+      <c r="G106"/>
+      <c r="H106"/>
+      <c r="I106"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>19</v>
+      </c>
+      <c r="B107" t="s">
+        <v>19</v>
+      </c>
+      <c r="C107" t="s">
+        <v>29</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-0.0554750139169474</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.590222928822899</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.831361299855504</v>
+      </c>
+      <c r="G107"/>
+      <c r="H107"/>
+      <c r="I107"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>20</v>
+      </c>
+      <c r="B108" t="s">
+        <v>20</v>
+      </c>
+      <c r="C108" t="s">
+        <v>29</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.11642979309734</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.258634732869426</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.517269465738852</v>
+      </c>
+      <c r="G108"/>
+      <c r="H108"/>
+      <c r="I108"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>21</v>
+      </c>
+      <c r="B109" t="s">
+        <v>21</v>
+      </c>
+      <c r="C109" t="s">
+        <v>29</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-0.152355125779557</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.139552019518648</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.418656058555944</v>
+      </c>
+      <c r="G109"/>
+      <c r="H109"/>
+      <c r="I109"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2767,19 +3086,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
@@ -2788,21 +3107,21 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -2811,26 +3130,26 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.116062165812614</v>
+        <v>0.127191848392785</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
       <c r="I2" t="n">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -2839,82 +3158,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0138594053081593</v>
+        <v>0.0205059050658457</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
       <c r="I3" t="n">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="J3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00692506393730139</v>
+        <v>0.0372686188618791</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
       <c r="I4" t="n">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="J4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0144880606336468</v>
+        <v>0.0200988864856963</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
       <c r="I5" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="J5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -2923,26 +3242,26 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0883617586478161</v>
+        <v>0.0621507392549162</v>
       </c>
       <c r="G6"/>
       <c r="H6"/>
       <c r="I6" t="n">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="J6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2951,110 +3270,110 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.212768837336716</v>
+        <v>0.0803351456903422</v>
       </c>
       <c r="G7"/>
       <c r="H7"/>
       <c r="I7" t="n">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="J7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0204071679468525</v>
+        <v>0.0635809801719385</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
       <c r="I8" t="n">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="J8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0208598776799607</v>
+        <v>0.175871232820493</v>
       </c>
       <c r="G9"/>
       <c r="H9"/>
       <c r="I9" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="J9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.17349609883131</v>
+        <v>0.0155867197126552</v>
       </c>
       <c r="G10"/>
       <c r="H10"/>
       <c r="I10" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -3063,12 +3382,12 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0952805350550737</v>
+        <v>0.165463982982672</v>
       </c>
       <c r="G11"/>
       <c r="H11"/>
       <c r="I11" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="J11" t="s">
         <v>62</v>
@@ -3076,7 +3395,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>63</v>
@@ -3091,15 +3410,43 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.186033723986584</v>
+        <v>0.280260856494352</v>
       </c>
       <c r="G12"/>
       <c r="H12"/>
       <c r="I12" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="J12" t="s">
         <v>65</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.245985886443367</v>
+      </c>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13" t="n">
+        <v>58</v>
+      </c>
+      <c r="J13" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -3138,292 +3485,308 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.17425092658077</v>
+        <v>0.106679111156521</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0204071679468525</v>
+        <v>0.159814159212223</v>
       </c>
       <c r="F2" t="n">
-        <v>0.224478847415378</v>
+        <v>0.351742465640986</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
+      <c r="I2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
       <c r="D3" t="n">
-        <v>0.00461843191688611</v>
+        <v>0.0164998065356796</v>
       </c>
       <c r="E3" t="n">
-        <v>0.950840679229933</v>
+        <v>0.827709455629325</v>
       </c>
       <c r="F3" t="n">
-        <v>0.960146595097477</v>
+        <v>0.978294435788638</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
+      <c r="I3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.145404468260077</v>
+        <v>0.00065224547308039</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0527756256599646</v>
+        <v>0.993135371570823</v>
       </c>
       <c r="F4" t="n">
-        <v>0.255336764787751</v>
+        <v>0.993135371570823</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
+      <c r="I4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.119870424819134</v>
+        <v>0.0840181310144708</v>
       </c>
       <c r="E5" t="n">
-        <v>0.110095794873296</v>
+        <v>0.268060550348461</v>
       </c>
       <c r="F5" t="n">
-        <v>0.255336764787751</v>
+        <v>0.459532372025933</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
+      <c r="I5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0695662929791277</v>
+        <v>0.0160367928499266</v>
       </c>
       <c r="E6" t="n">
-        <v>0.35331903045467</v>
+        <v>0.832471279931623</v>
       </c>
       <c r="F6" t="n">
-        <v>0.485813666875172</v>
+        <v>0.978294435788638</v>
       </c>
       <c r="G6"/>
       <c r="H6"/>
+      <c r="I6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.102069989661726</v>
+        <v>0.00983594256126937</v>
       </c>
       <c r="E7" t="n">
-        <v>0.17349609883131</v>
+        <v>0.896769899472918</v>
       </c>
       <c r="F7" t="n">
-        <v>0.318076181190734</v>
+        <v>0.978294435788638</v>
       </c>
       <c r="G7"/>
       <c r="H7"/>
+      <c r="I7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0182622226962919</v>
+        <v>-0.102715834816381</v>
       </c>
       <c r="E8" t="n">
-        <v>0.807406522566315</v>
+        <v>0.175871232820493</v>
       </c>
       <c r="F8" t="n">
-        <v>0.960146595097477</v>
+        <v>0.351742465640986</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
+      <c r="I8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>0.125170010431124</v>
+        <v>0.1052517143198</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0952805350550737</v>
+        <v>0.165463982982672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.255336764787751</v>
+        <v>0.351742465640986</v>
       </c>
       <c r="G9"/>
       <c r="H9"/>
+      <c r="I9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0872939501086421</v>
+        <v>-0.118090119538363</v>
       </c>
       <c r="E10" t="n">
-        <v>0.244277496561677</v>
+        <v>0.119782193577689</v>
       </c>
       <c r="F10" t="n">
-        <v>0.383864637454063</v>
+        <v>0.351742465640986</v>
       </c>
       <c r="G10"/>
       <c r="H10"/>
+      <c r="I10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.117895785723807</v>
+        <v>0.0703905355048749</v>
       </c>
       <c r="E11" t="n">
-        <v>0.116062165812614</v>
+        <v>0.353365966225374</v>
       </c>
       <c r="F11" t="n">
-        <v>0.255336764787751</v>
+        <v>0.530048949338061</v>
       </c>
       <c r="G11"/>
       <c r="H11"/>
+      <c r="I11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0037433413698872</v>
+        <v>-0.115775266535295</v>
       </c>
       <c r="E12" t="n">
-        <v>0.960146595097477</v>
+        <v>0.127191848392785</v>
       </c>
       <c r="F12" t="n">
-        <v>0.960146595097477</v>
+        <v>0.351742465640986</v>
       </c>
       <c r="G12"/>
       <c r="H12"/>
+      <c r="I12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0887187279761334</v>
+        <v>0.17673132101363</v>
       </c>
       <c r="E13" t="n">
-        <v>0.202292779264323</v>
+        <v>0.0200988864856963</v>
       </c>
       <c r="F13" t="n">
-        <v>0.950327173765851</v>
+        <v>0.241186637828355</v>
       </c>
       <c r="G13"/>
       <c r="H13"/>
+      <c r="I13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00664479106411173</v>
+        <v>0.00620750615759553</v>
       </c>
       <c r="E14" t="n">
-        <v>0.923848085773366</v>
+        <v>0.929700041547618</v>
       </c>
       <c r="F14" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G14"/>
       <c r="H14"/>
+      <c r="I14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -3433,19 +3796,20 @@
         <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0113712482267952</v>
+        <v>0.00713761272197522</v>
       </c>
       <c r="E15" t="n">
-        <v>0.870063610774027</v>
+        <v>0.91920042888924</v>
       </c>
       <c r="F15" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G15"/>
       <c r="H15"/>
+      <c r="I15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -3455,19 +3819,20 @@
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.00433049874317533</v>
+        <v>0.0296371350882687</v>
       </c>
       <c r="E16" t="n">
-        <v>0.950327173765851</v>
+        <v>0.673630717139674</v>
       </c>
       <c r="F16" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G16"/>
       <c r="H16"/>
+      <c r="I16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -3477,19 +3842,20 @@
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0154778749012223</v>
+        <v>-0.036607693468954</v>
       </c>
       <c r="E17" t="n">
-        <v>0.823808406517541</v>
+        <v>0.602922594060989</v>
       </c>
       <c r="F17" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G17"/>
       <c r="H17"/>
+      <c r="I17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -3499,19 +3865,20 @@
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.00666295405271881</v>
+        <v>-0.0168770929595755</v>
       </c>
       <c r="E18" t="n">
-        <v>0.92364056880673</v>
+        <v>0.810443423226343</v>
       </c>
       <c r="F18" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G18"/>
       <c r="H18"/>
+      <c r="I18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -3521,19 +3888,20 @@
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0133069405380289</v>
+        <v>0.00513284709983518</v>
       </c>
       <c r="E19" t="n">
-        <v>0.848195058698829</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="F19" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G19"/>
       <c r="H19"/>
+      <c r="I19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -3543,19 +3911,20 @@
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D20" t="n">
-        <v>0.023496990295322</v>
+        <v>-0.00682196906601559</v>
       </c>
       <c r="E20" t="n">
-        <v>0.735369463411301</v>
+        <v>0.922762116749113</v>
       </c>
       <c r="F20" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G20"/>
       <c r="H20"/>
+      <c r="I20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -3565,19 +3934,20 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00479271567000719</v>
+        <v>0.0382418583576679</v>
       </c>
       <c r="E21" t="n">
-        <v>0.94503334984807</v>
+        <v>0.586842790792824</v>
       </c>
       <c r="F21" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G21"/>
       <c r="H21"/>
+      <c r="I21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
@@ -3587,19 +3957,20 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0207367056611498</v>
+        <v>-0.00735778018481538</v>
       </c>
       <c r="E22" t="n">
-        <v>0.765481190564536</v>
+        <v>0.916717041909098</v>
       </c>
       <c r="F22" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G22"/>
       <c r="H22"/>
+      <c r="I22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
@@ -3609,1713 +3980,1998 @@
         <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0177842856521897</v>
+        <v>0.0165351194725005</v>
       </c>
       <c r="E23" t="n">
-        <v>0.798086166305484</v>
+        <v>0.814213193755719</v>
       </c>
       <c r="F23" t="n">
-        <v>0.950327173765851</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G23"/>
       <c r="H23"/>
+      <c r="I23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.134267572014771</v>
+        <v>-0.0185968615643766</v>
       </c>
       <c r="E24" t="n">
-        <v>0.071337504857376</v>
+        <v>0.79155391705199</v>
       </c>
       <c r="F24" t="n">
-        <v>0.156942510686227</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G24"/>
       <c r="H24"/>
+      <c r="I24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D25" t="n">
-        <v>0.138659313379964</v>
+        <v>0.0728360080369906</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0625927404040017</v>
+        <v>0.300869324970724</v>
       </c>
       <c r="F25" t="n">
-        <v>0.156942510686227</v>
+        <v>0.941846637807116</v>
       </c>
       <c r="G25"/>
       <c r="H25"/>
+      <c r="I25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.201537382986135</v>
+        <v>-0.0282479596820163</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00692506393730139</v>
+        <v>0.707281475434882</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0761757033103153</v>
+        <v>0.707281475434882</v>
       </c>
       <c r="G26"/>
       <c r="H26"/>
+      <c r="I26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0860009796394341</v>
+        <v>-0.174783134081328</v>
       </c>
       <c r="E27" t="n">
-        <v>0.24753585628794</v>
+        <v>0.0205059050658457</v>
       </c>
       <c r="F27" t="n">
-        <v>0.45381573652789</v>
+        <v>0.0823720753199149</v>
       </c>
       <c r="G27"/>
       <c r="H27"/>
+      <c r="I27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0756058703989498</v>
+        <v>0.157032962373461</v>
       </c>
       <c r="E28" t="n">
-        <v>0.309265558677127</v>
+        <v>0.0372686188618791</v>
       </c>
       <c r="F28" t="n">
-        <v>0.485988735064057</v>
+        <v>0.111805856585637</v>
       </c>
       <c r="G28"/>
       <c r="H28"/>
+      <c r="I28"/>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0580905756380288</v>
+        <v>-0.140563115139643</v>
       </c>
       <c r="E29" t="n">
-        <v>0.434562721128356</v>
+        <v>0.0621507392549162</v>
       </c>
       <c r="F29" t="n">
-        <v>0.531132214712436</v>
+        <v>0.149161774211799</v>
       </c>
       <c r="G29"/>
       <c r="H29"/>
+      <c r="I29"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D30" t="n">
-        <v>0.172240437979974</v>
+        <v>-0.0482262037767428</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0208598776799607</v>
+        <v>0.52152614633427</v>
       </c>
       <c r="F30" t="n">
-        <v>0.076486218159856</v>
+        <v>0.625831375601124</v>
       </c>
       <c r="G30"/>
       <c r="H30"/>
+      <c r="I30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.012242707258276</v>
+        <v>0.182486265530603</v>
       </c>
       <c r="E31" t="n">
-        <v>0.869149151821834</v>
+        <v>0.0155867197126552</v>
       </c>
       <c r="F31" t="n">
-        <v>0.869149151821834</v>
+        <v>0.0823720753199149</v>
       </c>
       <c r="G31"/>
       <c r="H31"/>
+      <c r="I31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.032247605111012</v>
+        <v>0.0616244307168021</v>
       </c>
       <c r="E32" t="n">
-        <v>0.664370598154253</v>
+        <v>0.412807914786857</v>
       </c>
       <c r="F32" t="n">
-        <v>0.730807657969679</v>
+        <v>0.550410553049142</v>
       </c>
       <c r="G32"/>
       <c r="H32"/>
+      <c r="I32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0663536601440665</v>
+        <v>0.0294183913497299</v>
       </c>
       <c r="E33" t="n">
-        <v>0.372145270872292</v>
+        <v>0.695748382816483</v>
       </c>
       <c r="F33" t="n">
-        <v>0.511699747449401</v>
+        <v>0.707281475434882</v>
       </c>
       <c r="G33"/>
       <c r="H33"/>
+      <c r="I33"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.182328952689138</v>
+        <v>0.0933746546791991</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0144880606336468</v>
+        <v>0.214852102760389</v>
       </c>
       <c r="F34" t="n">
-        <v>0.076486218159856</v>
+        <v>0.429704205520778</v>
       </c>
       <c r="G34"/>
       <c r="H34"/>
+      <c r="I34"/>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C35" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0229610877851472</v>
+        <v>-0.0859094248008704</v>
       </c>
       <c r="E35" t="n">
-        <v>0.741185386719181</v>
+        <v>0.253739403885517</v>
       </c>
       <c r="F35" t="n">
-        <v>0.815303925391099</v>
+        <v>0.434981835232315</v>
       </c>
       <c r="G35"/>
       <c r="H35"/>
+      <c r="I35"/>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D36" t="n">
-        <v>0.171674155243678</v>
+        <v>0.0638551652923891</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0138594053081593</v>
+        <v>0.396112031180432</v>
       </c>
       <c r="F36" t="n">
-        <v>0.152453458389753</v>
+        <v>0.550410553049142</v>
       </c>
       <c r="G36"/>
       <c r="H36"/>
+      <c r="I36"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C37" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D37" t="n">
-        <v>0.00616101253664516</v>
+        <v>-0.174662039385145</v>
       </c>
       <c r="E37" t="n">
-        <v>0.929377253711649</v>
+        <v>0.0205930188299787</v>
       </c>
       <c r="F37" t="n">
-        <v>0.929377253711649</v>
+        <v>0.0823720753199149</v>
       </c>
       <c r="G37"/>
       <c r="H37"/>
+      <c r="I37"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0877014718973078</v>
+        <v>0.130769293679604</v>
       </c>
       <c r="E38" t="n">
-        <v>0.207505651047244</v>
+        <v>0.0635809801719385</v>
       </c>
       <c r="F38" t="n">
-        <v>0.540898714652634</v>
+        <v>0.527193126890309</v>
       </c>
       <c r="G38"/>
       <c r="H38"/>
+      <c r="I38"/>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0435137770911641</v>
+        <v>-0.101639507795085</v>
       </c>
       <c r="E39" t="n">
-        <v>0.531432234719305</v>
+        <v>0.149043568699856</v>
       </c>
       <c r="F39" t="n">
-        <v>0.751880675854233</v>
+        <v>0.596174274799422</v>
       </c>
       <c r="G39"/>
       <c r="H39"/>
+      <c r="I39"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0390834897963618</v>
+        <v>0.12027851759581</v>
       </c>
       <c r="E40" t="n">
-        <v>0.574028137538539</v>
+        <v>0.0878655211483848</v>
       </c>
       <c r="F40" t="n">
-        <v>0.751880675854233</v>
+        <v>0.527193126890309</v>
       </c>
       <c r="G40"/>
       <c r="H40"/>
+      <c r="I40"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D41" t="n">
-        <v>0.034950254340995</v>
+        <v>0.0405545434450909</v>
       </c>
       <c r="E41" t="n">
-        <v>0.615175098426191</v>
+        <v>0.564433489042099</v>
       </c>
       <c r="F41" t="n">
-        <v>0.751880675854233</v>
+        <v>0.752577985389465</v>
       </c>
       <c r="G41"/>
       <c r="H41"/>
+      <c r="I41"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0807323044692387</v>
+        <v>0.0023391557339578</v>
       </c>
       <c r="E42" t="n">
-        <v>0.245863052114834</v>
+        <v>0.973479501870069</v>
       </c>
       <c r="F42" t="n">
-        <v>0.540898714652634</v>
+        <v>0.973479501870069</v>
       </c>
       <c r="G42"/>
       <c r="H42"/>
+      <c r="I42"/>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B43" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D43" t="n">
-        <v>0.086693100125935</v>
+        <v>0.0525217862080328</v>
       </c>
       <c r="E43" t="n">
-        <v>0.212768837336716</v>
+        <v>0.455528287866432</v>
       </c>
       <c r="F43" t="n">
-        <v>0.540898714652634</v>
+        <v>0.752577985389465</v>
       </c>
       <c r="G43"/>
       <c r="H43"/>
+      <c r="I43"/>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0521917982384489</v>
+        <v>0.04523826678797</v>
       </c>
       <c r="E44" t="n">
-        <v>0.452920807250981</v>
+        <v>0.520356892504631</v>
       </c>
       <c r="F44" t="n">
-        <v>0.751880675854233</v>
+        <v>0.752577985389465</v>
       </c>
       <c r="G44"/>
       <c r="H44"/>
+      <c r="I44"/>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.109832299275072</v>
+        <v>0.0430142920971172</v>
       </c>
       <c r="E45" t="n">
-        <v>0.114636651070569</v>
+        <v>0.541062142586273</v>
       </c>
       <c r="F45" t="n">
-        <v>0.540898714652634</v>
+        <v>0.752577985389465</v>
       </c>
       <c r="G45"/>
       <c r="H45"/>
+      <c r="I45"/>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.0824913161283707</v>
+        <v>-0.0870395789449637</v>
       </c>
       <c r="E46" t="n">
-        <v>0.281157166697679</v>
+        <v>0.216452007158174</v>
       </c>
       <c r="F46" t="n">
-        <v>0.817821017702153</v>
+        <v>0.649356021474523</v>
       </c>
       <c r="G46"/>
       <c r="H46"/>
+      <c r="I46"/>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B47" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0380302779130285</v>
+        <v>-0.030434410883923</v>
       </c>
       <c r="E47" t="n">
-        <v>0.619105171121224</v>
+        <v>0.665379442333905</v>
       </c>
       <c r="F47" t="n">
-        <v>0.817821017702153</v>
+        <v>0.798455330800687</v>
       </c>
       <c r="G47"/>
       <c r="H47"/>
+      <c r="I47"/>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.0479359899891019</v>
+        <v>-0.0525746278049512</v>
       </c>
       <c r="E48" t="n">
-        <v>0.530954309851595</v>
+        <v>0.455075235643833</v>
       </c>
       <c r="F48" t="n">
-        <v>0.817821017702153</v>
+        <v>0.752577985389465</v>
       </c>
       <c r="G48"/>
       <c r="H48"/>
+      <c r="I48"/>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B49" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0664936558031391</v>
+        <v>-0.0223069136055875</v>
       </c>
       <c r="E49" t="n">
-        <v>0.384888103779534</v>
+        <v>0.751232738856985</v>
       </c>
       <c r="F49" t="n">
-        <v>0.817821017702153</v>
+        <v>0.81952662420762</v>
       </c>
       <c r="G49"/>
       <c r="H49"/>
+      <c r="I49"/>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C50" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.101254381201523</v>
+        <v>-0.0148843622656003</v>
       </c>
       <c r="E50" t="n">
-        <v>0.186033723986584</v>
+        <v>0.847308229565406</v>
       </c>
       <c r="F50" t="n">
-        <v>0.817821017702153</v>
+        <v>0.951676696031647</v>
       </c>
       <c r="G50"/>
       <c r="H50"/>
+      <c r="I50"/>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D51" t="n">
-        <v>0.055700183525113</v>
+        <v>-0.0518772222493833</v>
       </c>
       <c r="E51" t="n">
-        <v>0.466629583619688</v>
+        <v>0.502239528905025</v>
       </c>
       <c r="F51" t="n">
-        <v>0.817821017702153</v>
+        <v>0.922584841692793</v>
       </c>
       <c r="G51"/>
       <c r="H51"/>
+      <c r="I51"/>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0205292519744194</v>
+        <v>0.0453289188205259</v>
       </c>
       <c r="E52" t="n">
-        <v>0.788407708561996</v>
+        <v>0.557667863955496</v>
       </c>
       <c r="F52" t="n">
-        <v>0.817821017702153</v>
+        <v>0.922584841692793</v>
       </c>
       <c r="G52"/>
       <c r="H52"/>
+      <c r="I52"/>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B53" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.0248568094299941</v>
+        <v>0.00468438006438979</v>
       </c>
       <c r="E53" t="n">
-        <v>0.745221450791998</v>
+        <v>0.951676696031647</v>
       </c>
       <c r="F53" t="n">
-        <v>0.817821017702153</v>
+        <v>0.951676696031647</v>
       </c>
       <c r="G53"/>
       <c r="H53"/>
+      <c r="I53"/>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C54" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.0176199755287301</v>
+        <v>0.0506275924890334</v>
       </c>
       <c r="E54" t="n">
-        <v>0.817821017702153</v>
+        <v>0.512586742383027</v>
       </c>
       <c r="F54" t="n">
-        <v>0.817821017702153</v>
+        <v>0.922584841692793</v>
       </c>
       <c r="G54"/>
       <c r="H54"/>
+      <c r="I54"/>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B55" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C55" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0327548964787683</v>
+        <v>0.00484475146308899</v>
       </c>
       <c r="E55" t="n">
-        <v>0.668522347161275</v>
+        <v>0.950024466849225</v>
       </c>
       <c r="F55" t="n">
-        <v>0.817821017702153</v>
+        <v>0.951676696031647</v>
       </c>
       <c r="G55"/>
       <c r="H55"/>
+      <c r="I55"/>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B56" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C56" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.0398879738502371</v>
+        <v>0.0573564263286989</v>
       </c>
       <c r="E56" t="n">
-        <v>0.602091909135782</v>
+        <v>0.458210053214844</v>
       </c>
       <c r="F56" t="n">
-        <v>0.817821017702153</v>
+        <v>0.922584841692793</v>
       </c>
       <c r="G56"/>
       <c r="H56"/>
+      <c r="I56"/>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C57" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D57" t="n">
-        <v>0.00304088247626602</v>
+        <v>-0.0306300639225915</v>
       </c>
       <c r="E57" t="n">
-        <v>0.968299516204039</v>
+        <v>0.691938631269595</v>
       </c>
       <c r="F57" t="n">
-        <v>0.968299516204039</v>
+        <v>0.922584841692793</v>
       </c>
       <c r="G57"/>
       <c r="H57"/>
+      <c r="I57"/>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B58" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C58" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0360039187658029</v>
+        <v>0.0591895800604847</v>
       </c>
       <c r="E58" t="n">
-        <v>0.638017204278547</v>
+        <v>0.443979077373685</v>
       </c>
       <c r="F58" t="n">
-        <v>0.779798805229336</v>
+        <v>0.922584841692793</v>
       </c>
       <c r="G58"/>
       <c r="H58"/>
+      <c r="I58"/>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B59" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C59" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0860972300441796</v>
+        <v>-0.0881528900574695</v>
       </c>
       <c r="E59" t="n">
-        <v>0.260855560091162</v>
+        <v>0.25443820157249</v>
       </c>
       <c r="F59" t="n">
-        <v>0.779798805229336</v>
+        <v>0.922584841692793</v>
       </c>
       <c r="G59"/>
       <c r="H59"/>
+      <c r="I59"/>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.0490462702728194</v>
+        <v>0.0325143262666986</v>
       </c>
       <c r="E60" t="n">
-        <v>0.521633130972589</v>
+        <v>0.674050403715883</v>
       </c>
       <c r="F60" t="n">
-        <v>0.779798805229336</v>
+        <v>0.922584841692793</v>
       </c>
       <c r="G60"/>
       <c r="H60"/>
+      <c r="I60"/>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.0471659631236178</v>
+        <v>-0.0954318394594336</v>
       </c>
       <c r="E61" t="n">
-        <v>0.53771412692509</v>
+        <v>0.217355661629767</v>
       </c>
       <c r="F61" t="n">
-        <v>0.779798805229336</v>
+        <v>0.922584841692793</v>
       </c>
       <c r="G61"/>
       <c r="H61"/>
+      <c r="I61"/>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.0397068520838941</v>
+        <v>0.0855872427333253</v>
       </c>
       <c r="E62" t="n">
-        <v>0.603868400994964</v>
+        <v>0.268665968550084</v>
       </c>
       <c r="F62" t="n">
-        <v>0.779798805229336</v>
+        <v>0.876530916682701</v>
       </c>
       <c r="G62"/>
       <c r="H62"/>
+      <c r="I62"/>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C63" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0254845341326823</v>
+        <v>-0.042515028435679</v>
       </c>
       <c r="E63" t="n">
-        <v>0.739108082512013</v>
+        <v>0.582497583848994</v>
       </c>
       <c r="F63" t="n">
-        <v>0.813018890763214</v>
+        <v>0.876530916682701</v>
       </c>
       <c r="G63"/>
       <c r="H63"/>
+      <c r="I63"/>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0768162107058077</v>
+        <v>0.0163440292053376</v>
       </c>
       <c r="E64" t="n">
-        <v>0.315707331909155</v>
+        <v>0.832602132286803</v>
       </c>
       <c r="F64" t="n">
-        <v>0.779798805229336</v>
+        <v>0.912842521828395</v>
       </c>
       <c r="G64"/>
       <c r="H64"/>
+      <c r="I64"/>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B65" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0648812589099049</v>
+        <v>0.125310204547815</v>
       </c>
       <c r="E65" t="n">
-        <v>0.39667468693565</v>
+        <v>0.105594594279685</v>
       </c>
       <c r="F65" t="n">
-        <v>0.779798805229336</v>
+        <v>0.876530916682701</v>
       </c>
       <c r="G65"/>
       <c r="H65"/>
+      <c r="I65"/>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C66" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.064404183583889</v>
+        <v>0.0835414782985354</v>
       </c>
       <c r="E66" t="n">
-        <v>0.400153048945474</v>
+        <v>0.280260856494352</v>
       </c>
       <c r="F66" t="n">
-        <v>0.779798805229336</v>
+        <v>0.876530916682701</v>
       </c>
       <c r="G66"/>
       <c r="H66"/>
+      <c r="I66"/>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B67" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C67" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.0539289181325395</v>
+        <v>0.00954784692452318</v>
       </c>
       <c r="E67" t="n">
-        <v>0.481065066356249</v>
+        <v>0.901729153445781</v>
       </c>
       <c r="F67" t="n">
-        <v>0.779798805229336</v>
+        <v>0.912842521828395</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
+      <c r="I67"/>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B68" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.108265601753358</v>
+        <v>-0.0385374394216661</v>
       </c>
       <c r="E68" t="n">
-        <v>0.157576284908472</v>
+        <v>0.618256840135387</v>
       </c>
       <c r="F68" t="n">
-        <v>0.346667826798639</v>
+        <v>0.876530916682701</v>
       </c>
       <c r="G68"/>
       <c r="H68"/>
+      <c r="I68"/>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C69" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D69" t="n">
-        <v>0.00298907690208906</v>
+        <v>0.0363797920395403</v>
       </c>
       <c r="E69" t="n">
-        <v>0.968839299111306</v>
+        <v>0.638048601066119</v>
       </c>
       <c r="F69" t="n">
-        <v>0.968839299111306</v>
+        <v>0.876530916682701</v>
       </c>
       <c r="G69"/>
       <c r="H69"/>
+      <c r="I69"/>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B70" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C70" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.121601165478601</v>
+        <v>-0.0515427592930625</v>
       </c>
       <c r="E70" t="n">
-        <v>0.112542877714915</v>
+        <v>0.505141010626103</v>
       </c>
       <c r="F70" t="n">
-        <v>0.309492913716018</v>
+        <v>0.876530916682701</v>
       </c>
       <c r="G70"/>
       <c r="H70"/>
+      <c r="I70"/>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B71" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C71" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D71" t="n">
-        <v>0.124656181263922</v>
+        <v>-0.0342974740250952</v>
       </c>
       <c r="E71" t="n">
-        <v>0.103819433855277</v>
+        <v>0.657398187512026</v>
       </c>
       <c r="F71" t="n">
-        <v>0.309492913716018</v>
+        <v>0.876530916682701</v>
       </c>
       <c r="G71"/>
       <c r="H71"/>
+      <c r="I71"/>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C72" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.0792580564314036</v>
+        <v>-0.0646640787042194</v>
       </c>
       <c r="E72" t="n">
-        <v>0.300588282377239</v>
+        <v>0.403176861067897</v>
       </c>
       <c r="F72" t="n">
-        <v>0.551078517691606</v>
+        <v>0.876530916682701</v>
       </c>
       <c r="G72"/>
       <c r="H72"/>
+      <c r="I72"/>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B73" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C73" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.0206997662422272</v>
+        <v>0.00846347351720542</v>
       </c>
       <c r="E73" t="n">
-        <v>0.786765779684009</v>
+        <v>0.912842521828395</v>
       </c>
       <c r="F73" t="n">
-        <v>0.916027362498677</v>
+        <v>0.912842521828395</v>
       </c>
       <c r="G73"/>
       <c r="H73"/>
+      <c r="I73"/>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C74" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D74" t="n">
-        <v>0.162774717771661</v>
+        <v>-0.0734300106282945</v>
       </c>
       <c r="E74" t="n">
-        <v>0.033861927042385</v>
+        <v>0.342527989573741</v>
       </c>
       <c r="F74" t="n">
-        <v>0.309492913716018</v>
+        <v>0.671068819551934</v>
       </c>
       <c r="G74"/>
       <c r="H74"/>
+      <c r="I74"/>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C75" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.016158801021707</v>
+        <v>-0.115658654721923</v>
       </c>
       <c r="E75" t="n">
-        <v>0.83275214772607</v>
+        <v>0.13518077973217</v>
       </c>
       <c r="F75" t="n">
-        <v>0.916027362498677</v>
+        <v>0.405542339196511</v>
       </c>
       <c r="G75"/>
       <c r="H75"/>
+      <c r="I75"/>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C76" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.0540594463270421</v>
+        <v>0.0530984739829882</v>
       </c>
       <c r="E76" t="n">
-        <v>0.480004729514559</v>
+        <v>0.492380681121931</v>
       </c>
       <c r="F76" t="n">
-        <v>0.660006503082519</v>
+        <v>0.671068819551934</v>
       </c>
       <c r="G76"/>
       <c r="H76"/>
+      <c r="I76"/>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0541412747986264</v>
+        <v>-0.055807454036919</v>
       </c>
       <c r="E77" t="n">
-        <v>0.47934065424041</v>
+        <v>0.470581328112939</v>
       </c>
       <c r="F77" t="n">
-        <v>0.660006503082519</v>
+        <v>0.671068819551934</v>
       </c>
       <c r="G77"/>
       <c r="H77"/>
+      <c r="I77"/>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B78" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C78" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.126425571546606</v>
+        <v>0.0329761187878349</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0990190003951576</v>
+        <v>0.669798293359957</v>
       </c>
       <c r="F78" t="n">
-        <v>0.309492913716018</v>
+        <v>0.774525374998041</v>
       </c>
       <c r="G78"/>
       <c r="H78"/>
+      <c r="I78"/>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B79" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C79" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0855321986046367</v>
+        <v>0.139512326247094</v>
       </c>
       <c r="E79" t="n">
-        <v>0.402819725128278</v>
+        <v>0.0716830412962833</v>
       </c>
       <c r="F79" t="n">
-        <v>0.65950051515095</v>
+        <v>0.384311055119259</v>
       </c>
       <c r="G79"/>
       <c r="H79"/>
+      <c r="I79"/>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B80" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C80" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.00202635914722561</v>
+        <v>-0.022151275492834</v>
       </c>
       <c r="E80" t="n">
-        <v>0.984180550172677</v>
+        <v>0.774525374998041</v>
       </c>
       <c r="F80" t="n">
-        <v>0.984180550172677</v>
+        <v>0.774525374998041</v>
       </c>
       <c r="G80"/>
       <c r="H80"/>
+      <c r="I80"/>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B81" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C81" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D81" t="n">
-        <v>0.134033220033281</v>
+        <v>0.022783891292153</v>
       </c>
       <c r="E81" t="n">
-        <v>0.190124840249583</v>
+        <v>0.76826826393477</v>
       </c>
       <c r="F81" t="n">
-        <v>0.65950051515095</v>
+        <v>0.774525374998041</v>
       </c>
       <c r="G81"/>
       <c r="H81"/>
+      <c r="I81"/>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B82" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C82" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.115539926075959</v>
+        <v>0.1288714743311</v>
       </c>
       <c r="E82" t="n">
-        <v>0.258592783785286</v>
+        <v>0.0960777637798146</v>
       </c>
       <c r="F82" t="n">
-        <v>0.65950051515095</v>
+        <v>0.384311055119259</v>
       </c>
       <c r="G82"/>
       <c r="H82"/>
+      <c r="I82"/>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B83" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C83" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D83" t="n">
-        <v>0.0540884180779053</v>
+        <v>-0.0897724879420425</v>
       </c>
       <c r="E83" t="n">
-        <v>0.596686197717115</v>
+        <v>0.245985886443367</v>
       </c>
       <c r="F83" t="n">
-        <v>0.820443521861032</v>
+        <v>0.590366127464082</v>
       </c>
       <c r="G83"/>
       <c r="H83"/>
+      <c r="I83"/>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B84" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C84" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.0954070356090071</v>
+        <v>0.0517657143931209</v>
       </c>
       <c r="E84" t="n">
-        <v>0.35077381883406</v>
+        <v>0.503301614663951</v>
       </c>
       <c r="F84" t="n">
-        <v>0.65950051515095</v>
+        <v>0.671068819551934</v>
       </c>
       <c r="G84"/>
       <c r="H84"/>
+      <c r="I84"/>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B85" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C85" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D85" t="n">
-        <v>0.00495528215826297</v>
+        <v>-0.143891652262352</v>
       </c>
       <c r="E85" t="n">
-        <v>0.961327597329494</v>
+        <v>0.063245917851087</v>
       </c>
       <c r="F85" t="n">
-        <v>0.984180550172677</v>
+        <v>0.384311055119259</v>
       </c>
       <c r="G85"/>
       <c r="H85"/>
+      <c r="I85"/>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C86" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D86" t="n">
-        <v>0.101673020135802</v>
+        <v>0.100471604998926</v>
       </c>
       <c r="E86" t="n">
-        <v>0.320075462248847</v>
+        <v>0.331599736894066</v>
       </c>
       <c r="F86" t="n">
-        <v>0.65950051515095</v>
+        <v>0.708162829885467</v>
       </c>
       <c r="G86"/>
       <c r="H86"/>
+      <c r="I86"/>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B87" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C87" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D87" t="n">
-        <v>0.0825012344386349</v>
+        <v>0.00936219381370434</v>
       </c>
       <c r="E87" t="n">
-        <v>0.41968214600515</v>
+        <v>0.927877351922577</v>
       </c>
       <c r="F87" t="n">
-        <v>0.65950051515095</v>
+        <v>0.96373210668647</v>
       </c>
       <c r="G87"/>
       <c r="H87"/>
+      <c r="I87"/>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C88" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.0971590800626574</v>
+        <v>-0.0289848896151883</v>
       </c>
       <c r="E88" t="n">
-        <v>0.342007253225118</v>
+        <v>0.779307298309783</v>
       </c>
       <c r="F88" t="n">
-        <v>0.65950051515095</v>
+        <v>0.93516875797174</v>
       </c>
       <c r="G88"/>
       <c r="H88"/>
+      <c r="I88"/>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.0140409442823025</v>
+        <v>0.120625824483425</v>
       </c>
       <c r="E89" t="n">
-        <v>0.890722570103284</v>
+        <v>0.243858820361034</v>
       </c>
       <c r="F89" t="n">
-        <v>0.984180550172677</v>
+        <v>0.708162829885467</v>
       </c>
       <c r="G89"/>
       <c r="H89"/>
+      <c r="I89"/>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B90" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C90" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.111306484229624</v>
+        <v>0.0329138858095021</v>
       </c>
       <c r="E90" t="n">
-        <v>0.274367664727275</v>
+        <v>0.750330975512539</v>
       </c>
       <c r="F90" t="n">
-        <v>0.503007385333338</v>
+        <v>0.93516875797174</v>
       </c>
       <c r="G90"/>
       <c r="H90"/>
+      <c r="I90"/>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B91" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C91" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.0330148418637138</v>
+        <v>0.00470309546143418</v>
       </c>
       <c r="E91" t="n">
-        <v>0.745619496610592</v>
+        <v>0.96373210668647</v>
       </c>
       <c r="F91" t="n">
-        <v>0.827741812715881</v>
+        <v>0.96373210668647</v>
       </c>
       <c r="G91"/>
       <c r="H91"/>
+      <c r="I91"/>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B92" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C92" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.20769839552278</v>
+        <v>-0.095893865750365</v>
       </c>
       <c r="E92" t="n">
-        <v>0.0417360760492035</v>
+        <v>0.354081414942733</v>
       </c>
       <c r="F92" t="n">
-        <v>0.459096836541238</v>
+        <v>0.708162829885467</v>
       </c>
       <c r="G92"/>
       <c r="H92"/>
+      <c r="I92"/>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B93" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C93" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D93" t="n">
-        <v>0.173702451536742</v>
+        <v>0.0670098559621318</v>
       </c>
       <c r="E93" t="n">
-        <v>0.0883617586478161</v>
+        <v>0.517163614377893</v>
       </c>
       <c r="F93" t="n">
-        <v>0.485989672562989</v>
+        <v>0.886566196076388</v>
       </c>
       <c r="G93"/>
       <c r="H93"/>
+      <c r="I93"/>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B94" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C94" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.0320920933077857</v>
+        <v>-0.110732339353547</v>
       </c>
       <c r="E94" t="n">
-        <v>0.752492557014437</v>
+        <v>0.284648787287383</v>
       </c>
       <c r="F94" t="n">
-        <v>0.827741812715881</v>
+        <v>0.708162829885467</v>
       </c>
       <c r="G94"/>
       <c r="H94"/>
+      <c r="I94"/>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B95" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C95" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D95" t="n">
-        <v>0.0190070858416669</v>
+        <v>0.0538554160323744</v>
       </c>
       <c r="E95" t="n">
-        <v>0.851832312336532</v>
+        <v>0.602636367404753</v>
       </c>
       <c r="F95" t="n">
-        <v>0.851832312336532</v>
+        <v>0.903954551107129</v>
       </c>
       <c r="G95"/>
       <c r="H95"/>
+      <c r="I95"/>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C96" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D96" t="n">
-        <v>0.137290183638979</v>
+        <v>-0.097178404970918</v>
       </c>
       <c r="E96" t="n">
-        <v>0.177742871318337</v>
+        <v>0.347677514706437</v>
       </c>
       <c r="F96" t="n">
-        <v>0.503007385333338</v>
+        <v>0.708162829885467</v>
       </c>
       <c r="G96"/>
       <c r="H96"/>
+      <c r="I96"/>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B97" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C97" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.0929750117275147</v>
+        <v>0.103895312976639</v>
       </c>
       <c r="E97" t="n">
-        <v>0.361120643427405</v>
+        <v>0.315404517029433</v>
       </c>
       <c r="F97" t="n">
-        <v>0.567475296814493</v>
+        <v>0.708162829885467</v>
       </c>
       <c r="G97"/>
       <c r="H97"/>
+      <c r="I97"/>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B98" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C98" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.118940705236947</v>
+        <v>-0.15901725336162</v>
       </c>
       <c r="E98" t="n">
-        <v>0.242841351016825</v>
+        <v>0.123096282731459</v>
       </c>
       <c r="F98" t="n">
-        <v>0.503007385333338</v>
+        <v>0.418656058555944</v>
       </c>
       <c r="G98"/>
       <c r="H98"/>
+      <c r="I98"/>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B99" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C99" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D99" t="n">
-        <v>0.118545458382515</v>
+        <v>-0.0731436262862439</v>
       </c>
       <c r="E99" t="n">
-        <v>0.244408064073736</v>
+        <v>0.477737376897154</v>
       </c>
       <c r="F99" t="n">
-        <v>0.503007385333338</v>
+        <v>0.818978360395121</v>
       </c>
       <c r="G99"/>
       <c r="H99"/>
+      <c r="I99"/>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C100" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.0724966534140664</v>
+        <v>0.0367544447776506</v>
       </c>
       <c r="E100" t="n">
-        <v>0.476327162749557</v>
+        <v>0.721228266060265</v>
       </c>
       <c r="F100" t="n">
-        <v>0.654949848780641</v>
+        <v>0.865473919272318</v>
       </c>
       <c r="G100"/>
       <c r="H100"/>
+      <c r="I100"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>13</v>
+      </c>
+      <c r="B101" t="s">
+        <v>13</v>
+      </c>
+      <c r="C101" t="s">
+        <v>29</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-0.181117658584734</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.0791668720684252</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.418656058555944</v>
+      </c>
+      <c r="G101"/>
+      <c r="H101"/>
+      <c r="I101"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>14</v>
+      </c>
+      <c r="B102" t="s">
+        <v>14</v>
+      </c>
+      <c r="C102" t="s">
+        <v>29</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-0.0505653595107006</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.623520974891628</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.831361299855504</v>
+      </c>
+      <c r="G102"/>
+      <c r="H102"/>
+      <c r="I102"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>15</v>
+      </c>
+      <c r="C103" t="s">
+        <v>29</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.12996447932257</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.207406635967208</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.4977759263213</v>
+      </c>
+      <c r="G103"/>
+      <c r="H103"/>
+      <c r="I103"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>16</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="s">
+        <v>29</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.0163861639288321</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.873599509560133</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.894985223087413</v>
+      </c>
+      <c r="G104"/>
+      <c r="H104"/>
+      <c r="I104"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>17</v>
+      </c>
+      <c r="B105" t="s">
+        <v>17</v>
+      </c>
+      <c r="C105" t="s">
+        <v>29</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-0.0135959007473873</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.894985223087413</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.894985223087413</v>
+      </c>
+      <c r="G105"/>
+      <c r="H105"/>
+      <c r="I105"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>18</v>
+      </c>
+      <c r="B106" t="s">
+        <v>18</v>
+      </c>
+      <c r="C106" t="s">
+        <v>29</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.180414233624163</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.0803351456903422</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.418656058555944</v>
+      </c>
+      <c r="G106"/>
+      <c r="H106"/>
+      <c r="I106"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>19</v>
+      </c>
+      <c r="B107" t="s">
+        <v>19</v>
+      </c>
+      <c r="C107" t="s">
+        <v>29</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-0.0554750139169474</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.590222928822899</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.831361299855504</v>
+      </c>
+      <c r="G107"/>
+      <c r="H107"/>
+      <c r="I107"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>20</v>
+      </c>
+      <c r="B108" t="s">
+        <v>20</v>
+      </c>
+      <c r="C108" t="s">
+        <v>29</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.11642979309734</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.258634732869426</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.517269465738852</v>
+      </c>
+      <c r="G108"/>
+      <c r="H108"/>
+      <c r="I108"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>21</v>
+      </c>
+      <c r="B109" t="s">
+        <v>21</v>
+      </c>
+      <c r="C109" t="s">
+        <v>29</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-0.152355125779557</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.139552019518648</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.418656058555944</v>
+      </c>
+      <c r="G109"/>
+      <c r="H109"/>
+      <c r="I109"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
